--- a/株式会社カナリア/株式会社カナリア_LOIチェックリスト_261001.xlsx
+++ b/株式会社カナリア/株式会社カナリア_LOIチェックリスト_261001.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LOIチェックリスト" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOIチェックリスト'!$A$1:$D$62</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'LOIチェックリスト'!$A$1:$D$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -109,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -118,11 +118,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -131,9 +129,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -500,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D62"/>
+  <dimension ref="A1:D61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21.6" customWidth="1" min="1" max="1"/>
@@ -516,12 +513,12 @@
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>準備物</t>
         </is>
       </c>
-      <c r="D1" s="9" t="n"/>
+      <c r="D1" s="4" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -657,10 +654,10 @@
           <t>■概要</t>
         </is>
       </c>
-      <c r="B10" s="9" t="n"/>
+      <c r="B10" s="8" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>当社のポジション</t>
         </is>
@@ -673,7 +670,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>契約類型</t>
         </is>
@@ -686,7 +683,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>ひな形</t>
         </is>
@@ -698,7 +695,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>案件フォルダURL</t>
         </is>
@@ -710,7 +707,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>案件チャンネルURL</t>
         </is>
@@ -722,7 +719,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>資料情報</t>
         </is>
@@ -741,10 +738,10 @@
           <t>■当事者情報</t>
         </is>
       </c>
-      <c r="B17" s="9" t="n"/>
+      <c r="B17" s="8" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>対象会社</t>
         </is>
@@ -761,7 +758,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>株主構成</t>
         </is>
@@ -774,7 +771,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>譲受企業</t>
         </is>
@@ -787,7 +784,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>機関設計</t>
         </is>
@@ -799,7 +796,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>役員構成</t>
         </is>
@@ -819,10 +816,10 @@
           <t>■株式情報</t>
         </is>
       </c>
-      <c r="B23" s="9" t="n"/>
+      <c r="B23" s="8" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>発行可能株式総数</t>
         </is>
@@ -834,7 +831,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>発行済株式総数</t>
         </is>
@@ -846,7 +843,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>株券／譲渡制限</t>
         </is>
@@ -859,7 +856,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>スキーム</t>
         </is>
@@ -882,10 +879,10 @@
           <t>■譲渡対価</t>
         </is>
       </c>
-      <c r="B28" s="9" t="n"/>
+      <c r="B28" s="8" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>譲渡対価総額</t>
         </is>
@@ -900,7 +897,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>希望額</t>
         </is>
@@ -915,52 +912,36 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>アーンアウト</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>☐なし　☑検討（B案）
-基準：2026年1月期 調整後EBITDA 45,877千円
-算定期間：2028年1月期（クロージング後最初に到来する事業年度）
-計算式：上限額×（達成率－80％）÷（100％－80％）／達成率80％以下は0円、100％以上は上限
-※調整後EBITDAの定義（経営指導料・配賦費用の取扱い）を●要確認</t>
-        </is>
-      </c>
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>■役員等の処遇</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>■役員等の処遇</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>役員</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>☐全員クロージング日に退任
 ☑一部留任（野口代表は譲受先にて継続勤務／期間7年程度・55歳まで）
 ☐全員留任
 ※役職名（代表取締役／取締役／取締役会長）・権限範囲・決裁権限規程は●要協議
-※中途退任時の取扱い（アーンアウト・インセンティブ）は●要協議</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+※中途退任時の業績連動賞与の取扱いは●要協議</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>役員報酬</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>ご希望：年額12,000千円以上
 2026年1月期実績：野口 紘 21,104千円
@@ -969,29 +950,29 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>業績連動賞与</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>☑付与を想定（売主様よりご要望あり）
+算定基礎：対象会社の調整後EBITDA／基準値45,877千円（2026年1月期実績）
+基準値の超過額の一定割合を支給する設計
+※支給率・上限額・支給時期は●要協議（SPA締結までに確定）
+※支給形態（役員賞与／事前確定届出給与・業績連動給与）、ストックオプションの可否は●要協議</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>業績インセンティブ</t>
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>退職慰労金</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>☑付与を検討（売主様よりご要望あり）
-算定基礎：対象会社の調整後EBITDA／基準値45,877千円（2026年1月期実績）
-支給率：超過額×●％（例：20％）／上限：年額●,000千円／不支給：基準値の●％未満
-支給形態：役員賞与（業績連動給与・事前確定届出給与）
-※ストックオプション・株式報酬の可否は●要協議（税務上の取扱いを含む）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>退職慰労金</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>野口代表：継続勤務のため本件での支給なし（将来の退任時は別途協議）
 退任予定の取締役2名（野口 文枝氏・野口 聰江氏）：支給有無・金額・原資は●要確認
@@ -999,13 +980,13 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>従業員</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>正社員7名。株式譲渡のため雇用契約は対象会社に残置（原則転籍手続は不要）。
 雇用条件を維持しての継続雇用が譲渡の付帯条件（少なくとも●年間）。
@@ -1014,34 +995,34 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>■経営者保証</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="n"/>
+    </row>
     <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>■経営者保証</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>経営者保証の有無</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>☐あり
 ☑なし（●要確認：有利子負債187,808千円に係る個人保証・担保提供の有無をDDにて確認）</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>譲受企業の解除義務</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>☑解除義務あり（クロージング後●ヶ月以内）
 ☐努力義務あり
@@ -1049,21 +1030,21 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>■その他資産／負債</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="n"/>
+    </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>■その他資産／負債</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A41" s="9" t="inlineStr">
         <is>
           <t>特記事項</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>・現預金193,226千円・借入金187,808千円はいずれも全額を対象会社に残置　→　ネットキャッシュ＋5,418千円
 ・投資有価証券275,896千円・保険積立金43,327千円・前渡金（ホテル会員権）6,570千円・
@@ -1076,117 +1057,117 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>■スケジュール</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n"/>
+    </row>
     <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>■スケジュール</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>意向表明提出日</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>2026年10月9日（金）～10月13日（火・大安）予定
 ※論点整理資料記載の10月10日は土曜日のため　→　●要確認</t>
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>意向表明応諾〆切</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>2026年10月20日（火）予定　※ご応諾により独占交渉権発生</t>
+        </is>
+      </c>
+    </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>意向表明応諾〆切</t>
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>ＤＤ</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>2026年10月20日（火）予定　※ご応諾により独占交渉権発生</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>ＤＤ</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>2026年11月24日（火）～12月4日（金）／報告会 12月9日（水）
 （財務・税務・法務・労務・ビジネス）</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>最終契約締結日</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>2026年12月15日（火）※大安
 ※論点整理資料では「2027年12月中旬」と記載　→　2026年の誤記と判断（●要確認）</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
         <is>
           <t>会社分割手続</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>2026年12月16日～2027年2月5日（債権者保護手続1ヶ月以上を含む）
 分割期日（新設会社の設立登記）：2027年2月10日（水）</t>
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>クロージング日</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>2027年2月17日（水）※大安</t>
+        </is>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>クロージング日</t>
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>独占交渉期間</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>2027年2月17日（水）※大安</t>
+          <t>ご応諾日～2027年2月末日（延長は双方協議）</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>独占交渉期間</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>ご応諾日～2027年2月末日（延長は双方協議）</t>
-        </is>
-      </c>
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>■成功報酬の計上時期</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>■成功報酬の計上時期</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>成功報酬（譲渡）</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>【計上時期】AD締結日：20●/●/●締結
 ☐最終契約締結時　☐クロージング時（●要確認）
@@ -1196,13 +1177,13 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>成功報酬（譲受）</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>【計上時期】AD締結日：20●/●/●締結
 ☐最終契約締結時　☐クロージング時（●要確認）
@@ -1211,34 +1192,34 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>中間報酬</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>成功報酬の10％（最低額300万円）／成約時は成功報酬に充当
 ※会社分割を伴うため、別途お見積りの要否を●要確認</t>
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>■その他論点</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+    </row>
     <row r="55">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>■その他論点</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A55" s="9" t="inlineStr">
         <is>
           <t>COC・主要取引先</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>・版権元（㈱講談社・㈱アニプレックス・㈱KADOKAWA・㈱小学館集英社プロダクション等）との
 　商品化許諾契約：COC条項の有無、事前通知・承諾の要否を確認
@@ -1248,26 +1229,26 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>本社事務所</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>・東京都台東区東上野一丁目20番5号 サスガビル4階（延床115.7㎡・月額賃料436千円・敷金1,264千円）
 ・COC条項の有無／本件実行後の継続利用の可否を確認</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="9" t="inlineStr">
         <is>
           <t>業績動向</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>・2026年1月期は輸出売上の反落（158,489→34,727千円）を国内売上の伸長（285,379→387,747千円）が補い、
 　売上高422,475千円・営業利益58,514千円（利益率13.9％）を維持
@@ -1275,39 +1256,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>棚卸資産廃棄損</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>・6,723→17,217→19,845千円と3期連続で増加（調整後EBITDAでは営業費用として控除）
 ・「在庫を抱えない方針」との説明との整合を●要確認</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="9" t="inlineStr">
         <is>
           <t>属人性</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>・野口代表へのOEM窓口機能の集中、制作部長（勤続12年）の継続勤務が事業継続の前提
 ・承継計画（役員派遣の要否・時期、社内昇格）と従業員への開示タイミングを確認</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
         <is>
           <t>数値の齟齬</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>●要確認：役員報酬について、IM「株主及び役員」の退任予定2名合計3,588千円（文枝1,788＋聰江1,800）と、
 IM「財務ハイライト（P/L）」の調整項目「退任予定分の役員報酬」2026年1月期2,990千円に差異あり。
@@ -1316,13 +1297,13 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>引継ぎ</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>・野口代表が担うOEM事業の窓口業務（見積作成・スケジュール調整）、版権元・仕入先との折衝の
 　引継範囲・期間・対価を協議
@@ -1332,17 +1313,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A50:B50"/>
     <mergeCell ref="C1:D1"/>
-    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
